--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260817.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260817.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>72,125,221</t>
+          <t>70,428,198</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>70,428,198</t>
+          <t>72,125,221</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>261,540,538</t>
+          <t>4,170,235</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,170,235</t>
+          <t>261,540,538</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
